--- a/calendario_data.xlsx
+++ b/calendario_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2543E3BD-4E59-4FD4-855F-0C135B49E0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8CD4D76-071B-48F3-BE32-83AFE3776718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
   <si>
     <t>Evento</t>
   </si>
@@ -34,15 +34,6 @@
     <t>Habilitado</t>
   </si>
   <si>
-    <t>Prueba de RM (Sentadilla/PB)</t>
-  </si>
-  <si>
-    <t>2025-11-01</t>
-  </si>
-  <si>
-    <t>Test de 1RM</t>
-  </si>
-  <si>
     <t>Sí</t>
   </si>
   <si>
@@ -64,16 +55,25 @@
     <t>Revisión de Mes</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t xml:space="preserve">Prueba 400 metros x 12 </t>
   </si>
   <si>
-    <t xml:space="preserve">Bosque san carlos </t>
-  </si>
-  <si>
     <t>2025-11-21</t>
+  </si>
+  <si>
+    <t>Seminario juzgamiento</t>
+  </si>
+  <si>
+    <t>Escuela aguila de oro</t>
+  </si>
+  <si>
+    <t>Por definir</t>
+  </si>
+  <si>
+    <t>Concentración (Eje cafetero)</t>
+  </si>
+  <si>
+    <t>Crioterapia</t>
   </si>
 </sst>
 </file>
@@ -135,11 +135,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -442,13 +443,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -467,16 +467,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -490,7 +490,7 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -501,24 +501,52 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2">
+        <v>45977</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45981</v>
+      </c>
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
+      <c r="B7" s="2">
+        <v>45991</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/calendario_data.xlsx
+++ b/calendario_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8CD4D76-071B-48F3-BE32-83AFE3776718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E1D075-DC1E-4728-AFE7-B1FF6FAD9C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>Evento</t>
   </si>
@@ -37,15 +37,6 @@
     <t>Sí</t>
   </si>
   <si>
-    <t>Evaluación de Resistencia</t>
-  </si>
-  <si>
-    <t>2025-11-15</t>
-  </si>
-  <si>
-    <t>Test de Cooper o 5K</t>
-  </si>
-  <si>
     <t>Reunión de Equipo</t>
   </si>
   <si>
@@ -74,6 +65,15 @@
   </si>
   <si>
     <t>Crioterapia</t>
+  </si>
+  <si>
+    <t>Bosque san carlos</t>
+  </si>
+  <si>
+    <t>Prueba 5 km</t>
+  </si>
+  <si>
+    <t>Parque san cristobal</t>
   </si>
 </sst>
 </file>
@@ -467,13 +467,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
+        <v>16</v>
+      </c>
+      <c r="B2" s="2">
+        <v>45977</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -481,13 +481,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -495,10 +495,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
@@ -509,13 +509,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2">
         <v>45977</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
@@ -523,13 +523,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2">
         <v>45981</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
         <v>4</v>
@@ -537,13 +537,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2">
         <v>45991</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>

--- a/calendario_data.xlsx
+++ b/calendario_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E1D075-DC1E-4728-AFE7-B1FF6FAD9C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F941085C-8137-4974-A116-DEAB16E45F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>Evento</t>
   </si>
@@ -46,15 +46,6 @@
     <t>Revisión de Mes</t>
   </si>
   <si>
-    <t xml:space="preserve">Prueba 400 metros x 12 </t>
-  </si>
-  <si>
-    <t>2025-11-21</t>
-  </si>
-  <si>
-    <t>Seminario juzgamiento</t>
-  </si>
-  <si>
     <t>Escuela aguila de oro</t>
   </si>
   <si>
@@ -67,13 +58,10 @@
     <t>Crioterapia</t>
   </si>
   <si>
-    <t>Bosque san carlos</t>
-  </si>
-  <si>
-    <t>Prueba 5 km</t>
-  </si>
-  <si>
-    <t>Parque san cristobal</t>
+    <t>Valoraciones UCAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCAD </t>
   </si>
 </sst>
 </file>
@@ -443,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" bestFit="1" customWidth="1"/>
@@ -467,13 +455,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="2">
-        <v>45977</v>
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -481,13 +469,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
+        <v>10</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45981</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -495,13 +483,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2">
+        <v>45991</v>
+      </c>
+      <c r="C4" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
@@ -509,43 +497,15 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2">
-        <v>45977</v>
+        <v>45975</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2">
-        <v>45981</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="2">
-        <v>45991</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
         <v>4</v>
       </c>
     </row>

--- a/calendario_data.xlsx
+++ b/calendario_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\APP DE GESTION DEPORTIVA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F941085C-8137-4974-A116-DEAB16E45F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{057BBB78-A9C4-4A05-9A9C-A661618AC0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
   <si>
     <t>Evento</t>
   </si>
@@ -49,9 +49,6 @@
     <t>Escuela aguila de oro</t>
   </si>
   <si>
-    <t>Por definir</t>
-  </si>
-  <si>
     <t>Concentración (Eje cafetero)</t>
   </si>
   <si>
@@ -61,7 +58,25 @@
     <t>Valoraciones UCAD</t>
   </si>
   <si>
-    <t xml:space="preserve">UCAD </t>
+    <t>Armenia - Quindio</t>
+  </si>
+  <si>
+    <t>UCAD (8:00 am -12:00 m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prueba Física </t>
+  </si>
+  <si>
+    <t>Parque Bosque san carlos</t>
+  </si>
+  <si>
+    <t>Parque San cristobal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparación Física </t>
+  </si>
+  <si>
+    <t>Cefe tunal ( por definir)</t>
   </si>
 </sst>
 </file>
@@ -431,12 +446,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -469,13 +485,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2">
-        <v>45981</v>
+        <v>45987</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -483,7 +499,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2">
         <v>45991</v>
@@ -497,7 +513,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2">
         <v>45975</v>
@@ -506,6 +522,48 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2">
+        <v>46015</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2">
+        <v>45975</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
         <v>4</v>
       </c>
     </row>
